--- a/rebalix-replica-archivio/snapshots/2026-08-13/basket-xspu.xlsx
+++ b/rebalix-replica-archivio/snapshots/2026-08-13/basket-xspu.xlsx
@@ -6,7 +6,7 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="2026-08-13" sheetId="2" r:id="Rd1eb2f0c6a24449f"/>
+    <x:sheet name="2026-08-13" sheetId="2" r:id="Rfe3a3da533d9499c"/>
   </x:sheets>
 </x:workbook>
 </file>
